--- a/Rent_Roll_Dashboard.xlsx
+++ b/Rent_Roll_Dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Desktop\Local 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B8AF3A4-EF2F-472D-980F-AE324BB7080A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12511CC5-1C53-4965-9681-850F37DAC0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="47880" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
     <sheet name="Locales" sheetId="3" r:id="rId3"/>
+    <sheet name="Form1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Locales!$A$1:$AN$500</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="561">
   <si>
     <t>Estado</t>
   </si>
@@ -1705,7 +1706,25 @@
     <t>Ingresado</t>
   </si>
   <si>
+    <t>En trámite</t>
+  </si>
+  <si>
     <t>Servicios listos</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Hora de inicio</t>
+  </si>
+  <si>
+    <t>Hora de finalización</t>
+  </si>
+  <si>
+    <t>Correo electrónico</t>
+  </si>
+  <si>
+    <t>Nombre</t>
   </si>
 </sst>
 </file>
@@ -1877,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1930,11 +1949,28 @@
     <xf numFmtId="166" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="15">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2272,7 +2308,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-50C0-41FC-8A38-81CAC06A5DE4}"/>
+              <c16:uniqueId val="{00000000-1462-449E-8395-6FF727630D2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2542,7 +2578,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C634-4463-B11B-F9519436B724}"/>
+              <c16:uniqueId val="{00000000-383C-49BB-9DC4-F83222F2066A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2867,7 +2903,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5818-4F2E-84CD-6D09E8EE0827}"/>
+              <c16:uniqueId val="{00000000-3E57-44D5-A59C-A5C263B5BB34}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3027,7 +3063,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5818-4F2E-84CD-6D09E8EE0827}"/>
+              <c16:uniqueId val="{00000001-3E57-44D5-A59C-A5C263B5BB34}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3394,7 +3430,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-21BC-41D2-A14A-36CBE0FD0632}"/>
+              <c16:uniqueId val="{00000000-A16C-4083-A1B5-B4CC3A5C8CCC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3562,7 +3598,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-21BC-41D2-A14A-36CBE0FD0632}"/>
+              <c16:uniqueId val="{00000001-A16C-4083-A1B5-B4CC3A5C8CCC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3869,7 +3905,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-830D-4936-B920-C2BA0E14ADD6}"/>
+              <c16:uniqueId val="{00000000-4B1A-4367-8D21-7494D5024F73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3983,7 +4019,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-830D-4936-B920-C2BA0E14ADD6}"/>
+              <c16:uniqueId val="{00000001-4B1A-4367-8D21-7494D5024F73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4317,6 +4353,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F092B3B9-24A0-469C-B647-5B28A7808C5D}" name="Tabla1" displayName="Tabla1" ref="A1:E2" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{F092B3B9-24A0-469C-B647-5B28A7808C5D}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{44260BA2-3A0C-40C8-BF07-45A5ECB1715F}" name="ID" dataDxfId="4">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="id"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{79A4DA71-252A-487A-A3E7-C1E850E70E3A}" name="Hora de inicio" dataDxfId="3">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="startDate"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{2A95A187-BC81-4AA6-BA89-0B63A1261AB0}" name="Hora de finalización" dataDxfId="2">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="submitDate"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{6D4B3C7C-7129-4A1C-8044-F8BCC8B5B77A}" name="Correo electrónico" dataDxfId="1">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="responder"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{D2822F66-0056-4AD5-834E-BA286410AB77}" name="Nombre" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="responderName"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <extLst>
+    <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
+      <xlmsforms:msForm id="DQSIkWdsW0yxEjajBLZtrQAAAAAAAAAAAAZAAJd7q4NUQUZXOVZCMTFSUzU0T1JWQVdGTUxQMjNUMS4u" isFormConnected="1" maxResponseId="0" latestEventMarker="0">
+        <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>responder</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>responderName</xlmsforms:syncedQuestionId>
+      </xlmsforms:msForm>
+    </ext>
+  </extLst>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7033,7 +7124,9 @@
         <v>199</v>
       </c>
       <c r="AM9" s="25"/>
-      <c r="AN9" s="25"/>
+      <c r="AN9" s="25" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="10" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="23" t="s">
@@ -7163,7 +7256,9 @@
         <v>199</v>
       </c>
       <c r="AM10" s="25"/>
-      <c r="AN10" s="25"/>
+      <c r="AN10" s="25" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="23" t="s">
@@ -7292,8 +7387,12 @@
       <c r="AL11" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="AM11" s="25"/>
-      <c r="AN11" s="25"/>
+      <c r="AM11" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="AN11" s="25" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="23" t="s">
@@ -7423,7 +7522,9 @@
         <v>199</v>
       </c>
       <c r="AM12" s="25"/>
-      <c r="AN12" s="25"/>
+      <c r="AN12" s="25" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="23" t="s">
@@ -7548,8 +7649,12 @@
       <c r="AL13" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="AM13" s="25"/>
-      <c r="AN13" s="25"/>
+      <c r="AM13" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="AN13" s="25" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="23" t="s">
@@ -7677,7 +7782,9 @@
         <v>199</v>
       </c>
       <c r="AM14" s="25"/>
-      <c r="AN14" s="25"/>
+      <c r="AN14" s="25" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="23" t="s">
@@ -7804,8 +7911,12 @@
       <c r="AL15" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="AM15" s="25"/>
-      <c r="AN15" s="25"/>
+      <c r="AM15" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="AN15" s="25" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="23" t="s">
@@ -7931,7 +8042,9 @@
       <c r="AK16" s="25"/>
       <c r="AL16" s="25"/>
       <c r="AM16" s="25"/>
-      <c r="AN16" s="25"/>
+      <c r="AN16" s="25" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="17" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="23" t="s">
@@ -8054,8 +8167,12 @@
       <c r="AL17" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="AM17" s="25"/>
-      <c r="AN17" s="25"/>
+      <c r="AM17" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN17" s="25" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="18" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="23" t="s">
@@ -8178,8 +8295,12 @@
       <c r="AL18" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="AM18" s="25"/>
-      <c r="AN18" s="25"/>
+      <c r="AM18" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN18" s="25" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="19" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="23" t="s">
@@ -8303,9 +8424,11 @@
         <v>212</v>
       </c>
       <c r="AM19" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN19" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN19" s="25"/>
     </row>
     <row r="20" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="23" t="s">
@@ -8435,9 +8558,11 @@
       <c r="AK20" s="25"/>
       <c r="AL20" s="25"/>
       <c r="AM20" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN20" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN20" s="25"/>
     </row>
     <row r="21" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="23" t="s">
@@ -8567,9 +8692,11 @@
       <c r="AK21" s="25"/>
       <c r="AL21" s="25"/>
       <c r="AM21" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN21" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN21" s="25"/>
     </row>
     <row r="22" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="23" t="s">
@@ -8699,9 +8826,11 @@
       <c r="AK22" s="25"/>
       <c r="AL22" s="25"/>
       <c r="AM22" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN22" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN22" s="25"/>
     </row>
     <row r="23" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="23" t="s">
@@ -8831,9 +8960,11 @@
       <c r="AK23" s="25"/>
       <c r="AL23" s="25"/>
       <c r="AM23" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN23" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN23" s="25"/>
     </row>
     <row r="24" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="23" t="s">
@@ -8963,9 +9094,11 @@
       <c r="AK24" s="25"/>
       <c r="AL24" s="25"/>
       <c r="AM24" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN24" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN24" s="25"/>
     </row>
     <row r="25" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="23" t="s">
@@ -9095,10 +9228,10 @@
       <c r="AK25" s="25"/>
       <c r="AL25" s="25"/>
       <c r="AM25" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN25" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN25" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9229,10 +9362,10 @@
       <c r="AK26" s="25"/>
       <c r="AL26" s="25"/>
       <c r="AM26" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN26" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN26" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9361,10 +9494,10 @@
       <c r="AK27" s="25"/>
       <c r="AL27" s="25"/>
       <c r="AM27" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN27" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN27" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9493,10 +9626,10 @@
       <c r="AK28" s="25"/>
       <c r="AL28" s="25"/>
       <c r="AM28" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN28" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN28" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9625,10 +9758,10 @@
       <c r="AK29" s="25"/>
       <c r="AL29" s="25"/>
       <c r="AM29" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN29" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN29" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9757,10 +9890,10 @@
       <c r="AK30" s="25"/>
       <c r="AL30" s="25"/>
       <c r="AM30" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN30" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN30" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9891,10 +10024,10 @@
       <c r="AK31" s="25"/>
       <c r="AL31" s="25"/>
       <c r="AM31" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN31" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN31" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="32" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10024,11 +10157,9 @@
       <c r="AL32" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="AM32" s="25" t="s">
+      <c r="AM32" s="25"/>
+      <c r="AN32" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN32" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="33" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10158,11 +10289,9 @@
       <c r="AL33" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM33" s="25" t="s">
+      <c r="AM33" s="25"/>
+      <c r="AN33" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN33" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="34" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10292,11 +10421,9 @@
       <c r="AL34" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM34" s="25" t="s">
+      <c r="AM34" s="25"/>
+      <c r="AN34" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN34" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="35" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10422,11 +10549,9 @@
       <c r="AL35" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM35" s="25" t="s">
+      <c r="AM35" s="25"/>
+      <c r="AN35" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN35" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="36" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10552,11 +10677,9 @@
       <c r="AL36" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM36" s="25" t="s">
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN36" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="37" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10682,11 +10805,9 @@
       <c r="AL37" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM37" s="25" t="s">
+      <c r="AM37" s="25"/>
+      <c r="AN37" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN37" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="38" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10812,11 +10933,9 @@
       <c r="AL38" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM38" s="25" t="s">
+      <c r="AM38" s="25"/>
+      <c r="AN38" s="25" t="s">
         <v>553</v>
-      </c>
-      <c r="AN38" s="25" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="39" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -10942,10 +11061,10 @@
       <c r="AL39" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="AM39" s="25" t="s">
+      <c r="AM39" s="25"/>
+      <c r="AN39" s="25" t="s">
         <v>553</v>
       </c>
-      <c r="AN39" s="25"/>
     </row>
     <row r="40" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="23" t="s">
@@ -11196,7 +11315,9 @@
       <c r="AL41" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="AM41" s="25"/>
+      <c r="AM41" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN41" s="25"/>
     </row>
     <row r="42" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11322,7 +11443,9 @@
       </c>
       <c r="AK42" s="25"/>
       <c r="AL42" s="25"/>
-      <c r="AM42" s="25"/>
+      <c r="AM42" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN42" s="25"/>
     </row>
     <row r="43" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11446,7 +11569,9 @@
       </c>
       <c r="AK43" s="25"/>
       <c r="AL43" s="25"/>
-      <c r="AM43" s="25"/>
+      <c r="AM43" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN43" s="25"/>
     </row>
     <row r="44" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11570,7 +11695,9 @@
       </c>
       <c r="AK44" s="25"/>
       <c r="AL44" s="25"/>
-      <c r="AM44" s="25"/>
+      <c r="AM44" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN44" s="25"/>
     </row>
     <row r="45" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11694,7 +11821,9 @@
       </c>
       <c r="AK45" s="25"/>
       <c r="AL45" s="25"/>
-      <c r="AM45" s="25"/>
+      <c r="AM45" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN45" s="25"/>
     </row>
     <row r="46" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11818,7 +11947,9 @@
       </c>
       <c r="AK46" s="25"/>
       <c r="AL46" s="25"/>
-      <c r="AM46" s="25"/>
+      <c r="AM46" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN46" s="25"/>
     </row>
     <row r="47" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11942,7 +12073,9 @@
       </c>
       <c r="AK47" s="25"/>
       <c r="AL47" s="25"/>
-      <c r="AM47" s="25"/>
+      <c r="AM47" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN47" s="25"/>
     </row>
     <row r="48" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12066,7 +12199,9 @@
       </c>
       <c r="AK48" s="25"/>
       <c r="AL48" s="25"/>
-      <c r="AM48" s="25"/>
+      <c r="AM48" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN48" s="25"/>
     </row>
     <row r="49" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12190,7 +12325,9 @@
       </c>
       <c r="AK49" s="25"/>
       <c r="AL49" s="25"/>
-      <c r="AM49" s="25"/>
+      <c r="AM49" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN49" s="25"/>
     </row>
     <row r="50" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12314,7 +12451,9 @@
       </c>
       <c r="AK50" s="25"/>
       <c r="AL50" s="25"/>
-      <c r="AM50" s="25"/>
+      <c r="AM50" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN50" s="25"/>
     </row>
     <row r="51" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12440,7 +12579,9 @@
       </c>
       <c r="AK51" s="25"/>
       <c r="AL51" s="25"/>
-      <c r="AM51" s="25"/>
+      <c r="AM51" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN51" s="25"/>
     </row>
     <row r="52" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12564,7 +12705,9 @@
       </c>
       <c r="AK52" s="25"/>
       <c r="AL52" s="25"/>
-      <c r="AM52" s="25"/>
+      <c r="AM52" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN52" s="25"/>
     </row>
     <row r="53" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12688,7 +12831,9 @@
       <c r="AL53" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="AM53" s="25"/>
+      <c r="AM53" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN53" s="25"/>
     </row>
     <row r="54" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12812,7 +12957,9 @@
       <c r="AL54" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="AM54" s="25"/>
+      <c r="AM54" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN54" s="25"/>
     </row>
     <row r="55" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -12936,7 +13083,9 @@
       <c r="AL55" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="AM55" s="25"/>
+      <c r="AM55" s="25" t="s">
+        <v>555</v>
+      </c>
       <c r="AN55" s="25"/>
     </row>
     <row r="56" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -58522,38 +58671,38 @@
   </sheetData>
   <autoFilter ref="A1:AN500" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="E2:E500">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"Firmado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"Proceso Firma"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"Interesado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Libre"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F500">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"Confirmado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"Sin confirmar"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"Atrazo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AN500">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"En trámite"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"Ingresado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
       <formula>"Servicios listos"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58582,4 +58731,44 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6BCB4D-F35F-41EB-95DA-D40565878DAA}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="5" width="17.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="36" t="s">
+        <v>556</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>558</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>559</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>